--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115891354</v>
+        <v>115891135</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538463</v>
+        <v>538358</v>
       </c>
       <c r="R2" t="n">
-        <v>7235211</v>
+        <v>7235320</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115891212</v>
+        <v>115891239</v>
       </c>
       <c r="B3" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538282</v>
+        <v>538762</v>
       </c>
       <c r="R3" t="n">
-        <v>7235288</v>
+        <v>7235276</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115891195</v>
+        <v>115891357</v>
       </c>
       <c r="B4" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538796</v>
+        <v>538320</v>
       </c>
       <c r="R4" t="n">
-        <v>7235295</v>
+        <v>7235210</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,37 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115891170</v>
+        <v>115891208</v>
       </c>
       <c r="B5" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538314</v>
+        <v>538275</v>
       </c>
       <c r="R5" t="n">
-        <v>7235308</v>
+        <v>7235290</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1077,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115891250</v>
+        <v>115891151</v>
       </c>
       <c r="B6" t="n">
-        <v>104722</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538270</v>
+        <v>538349</v>
       </c>
       <c r="R6" t="n">
-        <v>7235272</v>
+        <v>7235315</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1230,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115891239</v>
+        <v>115891394</v>
       </c>
       <c r="B7" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538762</v>
+        <v>538608</v>
       </c>
       <c r="R7" t="n">
-        <v>7235276</v>
+        <v>7235196</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1319,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1341,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115891200</v>
+        <v>115891406</v>
       </c>
       <c r="B8" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538355</v>
+        <v>538705</v>
       </c>
       <c r="R8" t="n">
-        <v>7235292</v>
+        <v>7235192</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1430,7 +1395,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1452,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115891411</v>
+        <v>115891121</v>
       </c>
       <c r="B9" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538767</v>
+        <v>538448</v>
       </c>
       <c r="R9" t="n">
-        <v>7235188</v>
+        <v>7235329</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1541,7 +1501,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1563,15 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115891441</v>
+        <v>115891301</v>
       </c>
       <c r="B10" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538732</v>
+        <v>538447</v>
       </c>
       <c r="R10" t="n">
-        <v>7235164</v>
+        <v>7235257</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1652,7 +1607,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1677,12 +1632,7 @@
         <v>115891142</v>
       </c>
       <c r="B11" t="n">
-        <v>95523</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115891394</v>
+        <v>115891218</v>
       </c>
       <c r="B12" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>2014</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538608</v>
+        <v>538546</v>
       </c>
       <c r="R12" t="n">
-        <v>7235196</v>
+        <v>7235286</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1874,7 +1819,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1896,55 +1841,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115891383</v>
+        <v>115891170</v>
       </c>
       <c r="B13" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538395</v>
+        <v>538314</v>
       </c>
       <c r="R13" t="n">
-        <v>7235199</v>
+        <v>7235308</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1979,11 +1914,6 @@
           <t>2023-09-13</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1995,7 +1925,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2017,37 +1947,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115891121</v>
+        <v>115891205</v>
       </c>
       <c r="B14" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538448</v>
+        <v>538274</v>
       </c>
       <c r="R14" t="n">
-        <v>7235329</v>
+        <v>7235291</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2106,7 +2031,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2128,37 +2053,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115891401</v>
+        <v>115891327</v>
       </c>
       <c r="B15" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2168,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538386</v>
+        <v>538593</v>
       </c>
       <c r="R15" t="n">
-        <v>7235194</v>
+        <v>7235242</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2217,7 +2137,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2239,55 +2159,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115891382</v>
+        <v>115891226</v>
       </c>
       <c r="B16" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538457</v>
+        <v>538299</v>
       </c>
       <c r="R16" t="n">
-        <v>7235199</v>
+        <v>7235283</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2333,7 +2243,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2355,37 +2265,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115891406</v>
+        <v>115891441</v>
       </c>
       <c r="B17" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538705</v>
+        <v>538732</v>
       </c>
       <c r="R17" t="n">
-        <v>7235192</v>
+        <v>7235164</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2444,7 +2349,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2466,15 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115891301</v>
+        <v>115891195</v>
       </c>
       <c r="B18" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2482,21 +2382,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2506,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538447</v>
+        <v>538796</v>
       </c>
       <c r="R18" t="n">
-        <v>7235257</v>
+        <v>7235295</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2555,7 +2455,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2577,37 +2477,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115891327</v>
+        <v>115891200</v>
       </c>
       <c r="B19" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2617,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538593</v>
+        <v>538355</v>
       </c>
       <c r="R19" t="n">
-        <v>7235242</v>
+        <v>7235292</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2666,7 +2561,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2688,15 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115891218</v>
+        <v>115891309</v>
       </c>
       <c r="B20" t="n">
-        <v>91121</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,21 +2594,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2014</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2728,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538546</v>
+        <v>538482</v>
       </c>
       <c r="R20" t="n">
-        <v>7235286</v>
+        <v>7235254</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2777,7 +2667,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2799,15 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115891075</v>
+        <v>115891395</v>
       </c>
       <c r="B21" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,39 +2700,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538424</v>
+        <v>538761</v>
       </c>
       <c r="R21" t="n">
-        <v>7235347</v>
+        <v>7235195</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2882,11 +2762,6 @@
           <t>2023-09-13</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2898,7 +2773,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2920,15 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115891185</v>
+        <v>115891401</v>
       </c>
       <c r="B22" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2960,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538340</v>
+        <v>538386</v>
       </c>
       <c r="R22" t="n">
-        <v>7235299</v>
+        <v>7235194</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3009,7 +2879,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3031,15 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115891208</v>
+        <v>67152464</v>
       </c>
       <c r="B23" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,37 +2912,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Erikslund, Dikanäs, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538275</v>
+        <v>538858</v>
       </c>
       <c r="R23" t="n">
-        <v>7235290</v>
+        <v>7235106</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,12 +2971,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2017-08-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2017-08-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3117,40 +2987,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>6277</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115891151</v>
+        <v>115891075</v>
       </c>
       <c r="B24" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3158,34 +3014,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538349</v>
+        <v>538424</v>
       </c>
       <c r="R24" t="n">
-        <v>7235315</v>
+        <v>7235347</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3220,6 +3081,11 @@
           <t>2023-09-13</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3231,7 +3097,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3253,15 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115891309</v>
+        <v>115891383</v>
       </c>
       <c r="B25" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3269,34 +3130,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538482</v>
+        <v>538395</v>
       </c>
       <c r="R25" t="n">
-        <v>7235254</v>
+        <v>7235199</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3331,6 +3197,11 @@
           <t>2023-09-13</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre hackmärken</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3342,7 +3213,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3364,50 +3235,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115891395</v>
+        <v>115891382</v>
       </c>
       <c r="B26" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538761</v>
+        <v>538457</v>
       </c>
       <c r="R26" t="n">
-        <v>7235195</v>
+        <v>7235199</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3453,7 +3324,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3475,15 +3346,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115891135</v>
+        <v>115891158</v>
       </c>
       <c r="B27" t="n">
-        <v>95203</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,21 +3357,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3381,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538358</v>
+        <v>538366</v>
       </c>
       <c r="R27" t="n">
-        <v>7235320</v>
+        <v>7235312</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3564,7 +3430,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3586,15 +3452,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115891158</v>
+        <v>115891354</v>
       </c>
       <c r="B28" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,21 +3463,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3626,10 +3487,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538366</v>
+        <v>538463</v>
       </c>
       <c r="R28" t="n">
-        <v>7235312</v>
+        <v>7235211</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3675,7 +3536,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3697,37 +3558,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115891093</v>
+        <v>115891250</v>
       </c>
       <c r="B29" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3737,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538315</v>
+        <v>538270</v>
       </c>
       <c r="R29" t="n">
-        <v>7235343</v>
+        <v>7235272</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3786,7 +3642,7 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3801,339 +3657,6 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>115891205</v>
-      </c>
-      <c r="B30" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>538274</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7235291</v>
-      </c>
-      <c r="S30" t="n">
-        <v>5</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>6273</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>115891226</v>
-      </c>
-      <c r="B31" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>538299</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7235283</v>
-      </c>
-      <c r="S31" t="n">
-        <v>5</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>6264</t>
-        </is>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>115891357</v>
-      </c>
-      <c r="B32" t="n">
-        <v>90279</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>112</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Stjärntagging</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Asterodon ferruginosus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>538320</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7235210</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>6338</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>

--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2365,53 +2365,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115891382</v>
+        <v>135653739</v>
       </c>
       <c r="B17" t="n">
-        <v>5179</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Dikafallet, Dikaån, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538457</v>
+        <v>537660</v>
       </c>
       <c r="R17" t="n">
-        <v>7235199</v>
+        <v>7234804</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2435,12 +2438,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,75 +2459,71 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>6358</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891382</t>
+          <t>https://artportalen.se/Sighting/135653739</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115891158</v>
+        <v>115891382</v>
       </c>
       <c r="B18" t="n">
-        <v>58114</v>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538366</v>
+        <v>538457</v>
       </c>
       <c r="R18" t="n">
-        <v>7235312</v>
+        <v>7235199</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2565,7 +2569,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2586,16 +2590,16 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891158</t>
+          <t>https://artportalen.se/Sighting/115891382</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115891354</v>
+        <v>115891158</v>
       </c>
       <c r="B19" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2603,21 +2607,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2627,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538463</v>
+        <v>538366</v>
       </c>
       <c r="R19" t="n">
-        <v>7235211</v>
+        <v>7235312</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2697,38 +2701,38 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891354</t>
+          <t>https://artportalen.se/Sighting/115891158</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115891250</v>
+        <v>115891354</v>
       </c>
       <c r="B20" t="n">
-        <v>106229</v>
+        <v>58057</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2738,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538270</v>
+        <v>538463</v>
       </c>
       <c r="R20" t="n">
-        <v>7235272</v>
+        <v>7235211</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2787,7 +2791,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2808,38 +2812,38 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891250</t>
+          <t>https://artportalen.se/Sighting/115891354</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115891239</v>
+        <v>115891250</v>
       </c>
       <c r="B21" t="n">
-        <v>97358</v>
+        <v>106229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>221725</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538762</v>
+        <v>538270</v>
       </c>
       <c r="R21" t="n">
-        <v>7235276</v>
+        <v>7235272</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2898,7 +2902,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2919,54 +2923,66 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891239</t>
+          <t>https://artportalen.se/Sighting/115891250</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115891394</v>
+        <v>135653752</v>
       </c>
       <c r="B22" t="n">
-        <v>91905</v>
+        <v>99296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Dikafallet, Dikaån, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538608</v>
+        <v>537660</v>
       </c>
       <c r="R22" t="n">
-        <v>7235196</v>
+        <v>7234804</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,12 +3006,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,42 +3020,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>6521</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891394</t>
+          <t>https://artportalen.se/Sighting/135653752</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115891406</v>
+        <v>115891239</v>
       </c>
       <c r="B23" t="n">
-        <v>91905</v>
+        <v>97358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,21 +3055,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3079,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538705</v>
+        <v>538762</v>
       </c>
       <c r="R23" t="n">
-        <v>7235192</v>
+        <v>7235276</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,7 +3128,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3141,16 +3149,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891406</t>
+          <t>https://artportalen.se/Sighting/115891239</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115891218</v>
+        <v>115891394</v>
       </c>
       <c r="B24" t="n">
-        <v>92732</v>
+        <v>91905</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3158,21 +3166,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2014</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3182,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538546</v>
+        <v>538608</v>
       </c>
       <c r="R24" t="n">
-        <v>7235286</v>
+        <v>7235196</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3231,7 +3239,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3252,38 +3260,38 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891218</t>
+          <t>https://artportalen.se/Sighting/115891394</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115891327</v>
+        <v>115891406</v>
       </c>
       <c r="B25" t="n">
-        <v>91872</v>
+        <v>91905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3293,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538593</v>
+        <v>538705</v>
       </c>
       <c r="R25" t="n">
-        <v>7235242</v>
+        <v>7235192</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3342,7 +3350,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3363,38 +3371,38 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891327</t>
+          <t>https://artportalen.se/Sighting/115891406</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115891441</v>
+        <v>115891218</v>
       </c>
       <c r="B26" t="n">
-        <v>79327</v>
+        <v>92732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2014</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3404,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538732</v>
+        <v>538546</v>
       </c>
       <c r="R26" t="n">
-        <v>7235164</v>
+        <v>7235286</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3453,7 +3461,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3474,38 +3482,38 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891441</t>
+          <t>https://artportalen.se/Sighting/115891218</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115891195</v>
+        <v>115891327</v>
       </c>
       <c r="B27" t="n">
-        <v>83307</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538796</v>
+        <v>538593</v>
       </c>
       <c r="R27" t="n">
-        <v>7235295</v>
+        <v>7235242</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3564,7 +3572,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3585,38 +3593,38 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891195</t>
+          <t>https://artportalen.se/Sighting/115891327</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115891395</v>
+        <v>115891441</v>
       </c>
       <c r="B28" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3626,10 +3634,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538761</v>
+        <v>538732</v>
       </c>
       <c r="R28" t="n">
-        <v>7235195</v>
+        <v>7235164</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3675,7 +3683,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3696,16 +3704,16 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891395</t>
+          <t>https://artportalen.se/Sighting/115891441</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>67152464</v>
+        <v>115891195</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3713,42 +3721,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Erikslund, Dikanäs, Ås lm</t>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538858</v>
+        <v>538796</v>
       </c>
       <c r="R29" t="n">
-        <v>7235106</v>
+        <v>7235295</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3772,12 +3775,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2017-08-05</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2017-08-05</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3788,20 +3791,247 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>6483</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115891195</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>115891395</v>
+      </c>
+      <c r="B30" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>538761</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7235195</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>6495</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115891395</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>67152464</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Erikslund, Dikanäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>538858</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7235106</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2017-08-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2017-08-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr">
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/67152464</t>
         </is>
@@ -3837,6 +4067,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -2932,7 +2932,7 @@
         <v>135653752</v>
       </c>
       <c r="B22" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2365,56 +2365,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135653739</v>
+        <v>115891382</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>5179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dikafallet, Dikaån, Ås lm</t>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537660</v>
+        <v>538457</v>
       </c>
       <c r="R17" t="n">
-        <v>7234804</v>
+        <v>7235199</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,17 +2435,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2459,71 +2451,75 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>6358</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135653739</t>
+          <t>https://artportalen.se/Sighting/115891382</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115891382</v>
+        <v>115891158</v>
       </c>
       <c r="B18" t="n">
-        <v>5179</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538457</v>
+        <v>538366</v>
       </c>
       <c r="R18" t="n">
-        <v>7235199</v>
+        <v>7235312</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2569,7 +2565,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2590,16 +2586,16 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891382</t>
+          <t>https://artportalen.se/Sighting/115891158</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115891158</v>
+        <v>115891354</v>
       </c>
       <c r="B19" t="n">
-        <v>58114</v>
+        <v>58057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2607,21 +2603,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2627,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538366</v>
+        <v>538463</v>
       </c>
       <c r="R19" t="n">
-        <v>7235312</v>
+        <v>7235211</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2680,7 +2676,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2701,38 +2697,38 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891158</t>
+          <t>https://artportalen.se/Sighting/115891354</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115891354</v>
+        <v>115891250</v>
       </c>
       <c r="B20" t="n">
-        <v>58057</v>
+        <v>106229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2738,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538463</v>
+        <v>538270</v>
       </c>
       <c r="R20" t="n">
-        <v>7235211</v>
+        <v>7235272</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2791,7 +2787,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2812,38 +2808,38 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891354</t>
+          <t>https://artportalen.se/Sighting/115891250</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115891250</v>
+        <v>115891239</v>
       </c>
       <c r="B21" t="n">
-        <v>106229</v>
+        <v>97358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221725</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538270</v>
+        <v>538762</v>
       </c>
       <c r="R21" t="n">
-        <v>7235272</v>
+        <v>7235276</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2902,7 +2898,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2923,66 +2919,54 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891250</t>
+          <t>https://artportalen.se/Sighting/115891239</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135653752</v>
+        <v>115891394</v>
       </c>
       <c r="B22" t="n">
-        <v>99298</v>
+        <v>91905</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dikafallet, Dikaån, Ås lm</t>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537660</v>
+        <v>538608</v>
       </c>
       <c r="R22" t="n">
-        <v>7234804</v>
+        <v>7235196</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3006,12 +2990,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,34 +3004,42 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>6521</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135653752</t>
+          <t>https://artportalen.se/Sighting/115891394</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115891239</v>
+        <v>115891406</v>
       </c>
       <c r="B23" t="n">
-        <v>97358</v>
+        <v>91905</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,21 +3047,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3079,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538762</v>
+        <v>538705</v>
       </c>
       <c r="R23" t="n">
-        <v>7235276</v>
+        <v>7235192</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3128,7 +3120,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3149,16 +3141,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891239</t>
+          <t>https://artportalen.se/Sighting/115891406</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115891394</v>
+        <v>115891218</v>
       </c>
       <c r="B24" t="n">
-        <v>91905</v>
+        <v>92732</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3166,21 +3158,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>2014</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3190,10 +3182,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538608</v>
+        <v>538546</v>
       </c>
       <c r="R24" t="n">
-        <v>7235196</v>
+        <v>7235286</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3239,7 +3231,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3260,38 +3252,38 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891394</t>
+          <t>https://artportalen.se/Sighting/115891218</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115891406</v>
+        <v>115891327</v>
       </c>
       <c r="B25" t="n">
-        <v>91905</v>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3293,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538705</v>
+        <v>538593</v>
       </c>
       <c r="R25" t="n">
-        <v>7235192</v>
+        <v>7235242</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3350,7 +3342,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3371,38 +3363,38 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891406</t>
+          <t>https://artportalen.se/Sighting/115891327</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115891218</v>
+        <v>115891441</v>
       </c>
       <c r="B26" t="n">
-        <v>92732</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2014</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3412,10 +3404,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538546</v>
+        <v>538732</v>
       </c>
       <c r="R26" t="n">
-        <v>7235286</v>
+        <v>7235164</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3461,7 +3453,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3482,38 +3474,38 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891218</t>
+          <t>https://artportalen.se/Sighting/115891441</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115891327</v>
+        <v>115891195</v>
       </c>
       <c r="B27" t="n">
-        <v>91872</v>
+        <v>83307</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3523,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538593</v>
+        <v>538796</v>
       </c>
       <c r="R27" t="n">
-        <v>7235242</v>
+        <v>7235295</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3572,7 +3564,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3593,38 +3585,38 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891327</t>
+          <t>https://artportalen.se/Sighting/115891195</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115891441</v>
+        <v>115891395</v>
       </c>
       <c r="B28" t="n">
-        <v>79327</v>
+        <v>83307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3634,10 +3626,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538732</v>
+        <v>538761</v>
       </c>
       <c r="R28" t="n">
-        <v>7235164</v>
+        <v>7235195</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3683,7 +3675,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3704,16 +3696,16 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891441</t>
+          <t>https://artportalen.se/Sighting/115891395</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115891195</v>
+        <v>67152464</v>
       </c>
       <c r="B29" t="n">
-        <v>83307</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3721,37 +3713,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Erikslund, Dikanäs, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538796</v>
+        <v>538858</v>
       </c>
       <c r="R29" t="n">
-        <v>7235295</v>
+        <v>7235106</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,12 +3772,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2017-08-05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2017-08-05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3791,247 +3788,20 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>6483</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/115891195</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>115891395</v>
-      </c>
-      <c r="B30" t="n">
-        <v>83307</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>538761</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7235195</v>
-      </c>
-      <c r="S30" t="n">
-        <v>5</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>6495</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/115891395</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>67152464</v>
-      </c>
-      <c r="B31" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Erikslund, Dikanäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>538858</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7235106</v>
-      </c>
-      <c r="S31" t="n">
-        <v>25</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2017-08-05</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2017-08-05</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/67152464</t>
         </is>
@@ -4067,8 +3837,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2365,53 +2365,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115891382</v>
+        <v>135653739</v>
       </c>
       <c r="B17" t="n">
-        <v>5179</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Dikafallet, Dikaån, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538457</v>
+        <v>537660</v>
       </c>
       <c r="R17" t="n">
-        <v>7235199</v>
+        <v>7234804</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2435,12 +2438,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,75 +2459,71 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>6358</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891382</t>
+          <t>https://artportalen.se/Sighting/135653739</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115891158</v>
+        <v>115891382</v>
       </c>
       <c r="B18" t="n">
-        <v>58114</v>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538366</v>
+        <v>538457</v>
       </c>
       <c r="R18" t="n">
-        <v>7235312</v>
+        <v>7235199</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2565,7 +2569,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2586,16 +2590,16 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891158</t>
+          <t>https://artportalen.se/Sighting/115891382</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115891354</v>
+        <v>115891158</v>
       </c>
       <c r="B19" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2603,21 +2607,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2627,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538463</v>
+        <v>538366</v>
       </c>
       <c r="R19" t="n">
-        <v>7235211</v>
+        <v>7235312</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2697,38 +2701,38 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891354</t>
+          <t>https://artportalen.se/Sighting/115891158</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115891250</v>
+        <v>115891354</v>
       </c>
       <c r="B20" t="n">
-        <v>106229</v>
+        <v>58057</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2738,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538270</v>
+        <v>538463</v>
       </c>
       <c r="R20" t="n">
-        <v>7235272</v>
+        <v>7235211</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2787,7 +2791,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2808,38 +2812,38 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891250</t>
+          <t>https://artportalen.se/Sighting/115891354</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115891239</v>
+        <v>115891250</v>
       </c>
       <c r="B21" t="n">
-        <v>97358</v>
+        <v>106229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>221725</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538762</v>
+        <v>538270</v>
       </c>
       <c r="R21" t="n">
-        <v>7235276</v>
+        <v>7235272</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2898,7 +2902,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2919,54 +2923,66 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891239</t>
+          <t>https://artportalen.se/Sighting/115891250</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115891394</v>
+        <v>135653752</v>
       </c>
       <c r="B22" t="n">
-        <v>91905</v>
+        <v>99298</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Dikafallet, Dikaån, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538608</v>
+        <v>537660</v>
       </c>
       <c r="R22" t="n">
-        <v>7235196</v>
+        <v>7234804</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,12 +3006,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,42 +3020,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>6521</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891394</t>
+          <t>https://artportalen.se/Sighting/135653752</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115891406</v>
+        <v>115891239</v>
       </c>
       <c r="B23" t="n">
-        <v>91905</v>
+        <v>97358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,21 +3055,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3079,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538705</v>
+        <v>538762</v>
       </c>
       <c r="R23" t="n">
-        <v>7235192</v>
+        <v>7235276</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,7 +3128,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3141,16 +3149,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891406</t>
+          <t>https://artportalen.se/Sighting/115891239</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115891218</v>
+        <v>115891394</v>
       </c>
       <c r="B24" t="n">
-        <v>92732</v>
+        <v>91905</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3158,21 +3166,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2014</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3182,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538546</v>
+        <v>538608</v>
       </c>
       <c r="R24" t="n">
-        <v>7235286</v>
+        <v>7235196</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3231,7 +3239,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3252,38 +3260,38 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891218</t>
+          <t>https://artportalen.se/Sighting/115891394</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115891327</v>
+        <v>115891406</v>
       </c>
       <c r="B25" t="n">
-        <v>91872</v>
+        <v>91905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3293,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538593</v>
+        <v>538705</v>
       </c>
       <c r="R25" t="n">
-        <v>7235242</v>
+        <v>7235192</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3342,7 +3350,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3363,38 +3371,38 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891327</t>
+          <t>https://artportalen.se/Sighting/115891406</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115891441</v>
+        <v>115891218</v>
       </c>
       <c r="B26" t="n">
-        <v>79327</v>
+        <v>92732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2014</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3404,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538732</v>
+        <v>538546</v>
       </c>
       <c r="R26" t="n">
-        <v>7235164</v>
+        <v>7235286</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3453,7 +3461,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3474,38 +3482,38 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891441</t>
+          <t>https://artportalen.se/Sighting/115891218</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115891195</v>
+        <v>115891327</v>
       </c>
       <c r="B27" t="n">
-        <v>83307</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538796</v>
+        <v>538593</v>
       </c>
       <c r="R27" t="n">
-        <v>7235295</v>
+        <v>7235242</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3564,7 +3572,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3585,38 +3593,38 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891195</t>
+          <t>https://artportalen.se/Sighting/115891327</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115891395</v>
+        <v>115891441</v>
       </c>
       <c r="B28" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3626,10 +3634,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538761</v>
+        <v>538732</v>
       </c>
       <c r="R28" t="n">
-        <v>7235195</v>
+        <v>7235164</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3675,7 +3683,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3696,16 +3704,16 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891395</t>
+          <t>https://artportalen.se/Sighting/115891441</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>67152464</v>
+        <v>115891195</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3713,42 +3721,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Erikslund, Dikanäs, Ås lm</t>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538858</v>
+        <v>538796</v>
       </c>
       <c r="R29" t="n">
-        <v>7235106</v>
+        <v>7235295</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3772,12 +3775,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2017-08-05</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2017-08-05</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3788,20 +3791,247 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>6483</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115891195</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>115891395</v>
+      </c>
+      <c r="B30" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>538761</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7235195</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>6495</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115891395</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>67152464</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Erikslund, Dikanäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>538858</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7235106</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2017-08-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2017-08-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr">
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/67152464</t>
         </is>
@@ -3837,6 +4067,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -2368,7 +2368,7 @@
         <v>135653739</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>135653752</v>
       </c>
       <c r="B22" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2365,56 +2365,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135653739</v>
+        <v>115891382</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>5179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dikafallet, Dikaån, Ås lm</t>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537660</v>
+        <v>538457</v>
       </c>
       <c r="R17" t="n">
-        <v>7234804</v>
+        <v>7235199</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,17 +2435,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2459,71 +2451,75 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>6358</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135653739</t>
+          <t>https://artportalen.se/Sighting/115891382</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115891382</v>
+        <v>115891158</v>
       </c>
       <c r="B18" t="n">
-        <v>5179</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538457</v>
+        <v>538366</v>
       </c>
       <c r="R18" t="n">
-        <v>7235199</v>
+        <v>7235312</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2569,7 +2565,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2590,16 +2586,16 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891382</t>
+          <t>https://artportalen.se/Sighting/115891158</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115891158</v>
+        <v>115891354</v>
       </c>
       <c r="B19" t="n">
-        <v>58114</v>
+        <v>58057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2607,21 +2603,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2627,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538366</v>
+        <v>538463</v>
       </c>
       <c r="R19" t="n">
-        <v>7235312</v>
+        <v>7235211</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2680,7 +2676,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2701,38 +2697,38 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891158</t>
+          <t>https://artportalen.se/Sighting/115891354</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115891354</v>
+        <v>115891250</v>
       </c>
       <c r="B20" t="n">
-        <v>58057</v>
+        <v>106229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2738,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538463</v>
+        <v>538270</v>
       </c>
       <c r="R20" t="n">
-        <v>7235211</v>
+        <v>7235272</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2791,7 +2787,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2812,38 +2808,38 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891354</t>
+          <t>https://artportalen.se/Sighting/115891250</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115891250</v>
+        <v>115891239</v>
       </c>
       <c r="B21" t="n">
-        <v>106229</v>
+        <v>97358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221725</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538270</v>
+        <v>538762</v>
       </c>
       <c r="R21" t="n">
-        <v>7235272</v>
+        <v>7235276</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2902,7 +2898,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2923,66 +2919,54 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891250</t>
+          <t>https://artportalen.se/Sighting/115891239</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135653752</v>
+        <v>115891394</v>
       </c>
       <c r="B22" t="n">
-        <v>99315</v>
+        <v>91905</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dikafallet, Dikaån, Ås lm</t>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537660</v>
+        <v>538608</v>
       </c>
       <c r="R22" t="n">
-        <v>7234804</v>
+        <v>7235196</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3006,12 +2990,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,34 +3004,42 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>6521</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135653752</t>
+          <t>https://artportalen.se/Sighting/115891394</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115891239</v>
+        <v>115891406</v>
       </c>
       <c r="B23" t="n">
-        <v>97358</v>
+        <v>91905</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,21 +3047,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3079,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538762</v>
+        <v>538705</v>
       </c>
       <c r="R23" t="n">
-        <v>7235276</v>
+        <v>7235192</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3128,7 +3120,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3149,16 +3141,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891239</t>
+          <t>https://artportalen.se/Sighting/115891406</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115891394</v>
+        <v>115891218</v>
       </c>
       <c r="B24" t="n">
-        <v>91905</v>
+        <v>92732</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3166,21 +3158,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>2014</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3190,10 +3182,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538608</v>
+        <v>538546</v>
       </c>
       <c r="R24" t="n">
-        <v>7235196</v>
+        <v>7235286</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3239,7 +3231,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3260,38 +3252,38 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891394</t>
+          <t>https://artportalen.se/Sighting/115891218</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115891406</v>
+        <v>115891327</v>
       </c>
       <c r="B25" t="n">
-        <v>91905</v>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3293,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538705</v>
+        <v>538593</v>
       </c>
       <c r="R25" t="n">
-        <v>7235192</v>
+        <v>7235242</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3350,7 +3342,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3371,38 +3363,38 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891406</t>
+          <t>https://artportalen.se/Sighting/115891327</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115891218</v>
+        <v>115891441</v>
       </c>
       <c r="B26" t="n">
-        <v>92732</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2014</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3412,10 +3404,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538546</v>
+        <v>538732</v>
       </c>
       <c r="R26" t="n">
-        <v>7235286</v>
+        <v>7235164</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3461,7 +3453,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3482,38 +3474,38 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891218</t>
+          <t>https://artportalen.se/Sighting/115891441</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115891327</v>
+        <v>115891195</v>
       </c>
       <c r="B27" t="n">
-        <v>91872</v>
+        <v>83307</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3523,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538593</v>
+        <v>538796</v>
       </c>
       <c r="R27" t="n">
-        <v>7235242</v>
+        <v>7235295</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3572,7 +3564,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3593,38 +3585,38 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891327</t>
+          <t>https://artportalen.se/Sighting/115891195</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115891441</v>
+        <v>115891395</v>
       </c>
       <c r="B28" t="n">
-        <v>79327</v>
+        <v>83307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3634,10 +3626,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538732</v>
+        <v>538761</v>
       </c>
       <c r="R28" t="n">
-        <v>7235164</v>
+        <v>7235195</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3683,7 +3675,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3704,16 +3696,16 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891441</t>
+          <t>https://artportalen.se/Sighting/115891395</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115891195</v>
+        <v>67152464</v>
       </c>
       <c r="B29" t="n">
-        <v>83307</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3721,37 +3713,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Erikslund, Dikanäs, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538796</v>
+        <v>538858</v>
       </c>
       <c r="R29" t="n">
-        <v>7235295</v>
+        <v>7235106</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,12 +3772,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2017-08-05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2017-08-05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3791,247 +3788,20 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>6483</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/115891195</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>115891395</v>
-      </c>
-      <c r="B30" t="n">
-        <v>83307</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>538761</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7235195</v>
-      </c>
-      <c r="S30" t="n">
-        <v>5</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>6495</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/115891395</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>67152464</v>
-      </c>
-      <c r="B31" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Erikslund, Dikanäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>538858</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7235106</v>
-      </c>
-      <c r="S31" t="n">
-        <v>25</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2017-08-05</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2017-08-05</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/67152464</t>
         </is>
@@ -4067,8 +3837,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2365,53 +2365,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115891382</v>
+        <v>135653739</v>
       </c>
       <c r="B17" t="n">
-        <v>5179</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Dikafallet, Dikaån, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538457</v>
+        <v>537660</v>
       </c>
       <c r="R17" t="n">
-        <v>7235199</v>
+        <v>7234804</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2435,12 +2438,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,75 +2459,71 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>6358</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891382</t>
+          <t>https://artportalen.se/Sighting/135653739</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115891158</v>
+        <v>115891382</v>
       </c>
       <c r="B18" t="n">
-        <v>58114</v>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538366</v>
+        <v>538457</v>
       </c>
       <c r="R18" t="n">
-        <v>7235312</v>
+        <v>7235199</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2565,7 +2569,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2586,16 +2590,16 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891158</t>
+          <t>https://artportalen.se/Sighting/115891382</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115891354</v>
+        <v>115891158</v>
       </c>
       <c r="B19" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2603,21 +2607,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2627,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538463</v>
+        <v>538366</v>
       </c>
       <c r="R19" t="n">
-        <v>7235211</v>
+        <v>7235312</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2697,38 +2701,38 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891354</t>
+          <t>https://artportalen.se/Sighting/115891158</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115891250</v>
+        <v>115891354</v>
       </c>
       <c r="B20" t="n">
-        <v>106229</v>
+        <v>58057</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2738,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538270</v>
+        <v>538463</v>
       </c>
       <c r="R20" t="n">
-        <v>7235272</v>
+        <v>7235211</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2787,7 +2791,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2808,38 +2812,38 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891250</t>
+          <t>https://artportalen.se/Sighting/115891354</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115891239</v>
+        <v>115891250</v>
       </c>
       <c r="B21" t="n">
-        <v>97358</v>
+        <v>106229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>221725</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538762</v>
+        <v>538270</v>
       </c>
       <c r="R21" t="n">
-        <v>7235276</v>
+        <v>7235272</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2898,7 +2902,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2919,54 +2923,66 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891239</t>
+          <t>https://artportalen.se/Sighting/115891250</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115891394</v>
+        <v>135653752</v>
       </c>
       <c r="B22" t="n">
-        <v>91905</v>
+        <v>99315</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Dikafallet, Dikaån, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538608</v>
+        <v>537660</v>
       </c>
       <c r="R22" t="n">
-        <v>7235196</v>
+        <v>7234804</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,12 +3006,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,42 +3020,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>6521</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891394</t>
+          <t>https://artportalen.se/Sighting/135653752</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115891406</v>
+        <v>115891239</v>
       </c>
       <c r="B23" t="n">
-        <v>91905</v>
+        <v>97358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,21 +3055,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3079,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538705</v>
+        <v>538762</v>
       </c>
       <c r="R23" t="n">
-        <v>7235192</v>
+        <v>7235276</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,7 +3128,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3141,16 +3149,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891406</t>
+          <t>https://artportalen.se/Sighting/115891239</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115891218</v>
+        <v>115891394</v>
       </c>
       <c r="B24" t="n">
-        <v>92732</v>
+        <v>91905</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3158,21 +3166,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2014</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3182,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538546</v>
+        <v>538608</v>
       </c>
       <c r="R24" t="n">
-        <v>7235286</v>
+        <v>7235196</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3231,7 +3239,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3252,38 +3260,38 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891218</t>
+          <t>https://artportalen.se/Sighting/115891394</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115891327</v>
+        <v>115891406</v>
       </c>
       <c r="B25" t="n">
-        <v>91872</v>
+        <v>91905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3293,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538593</v>
+        <v>538705</v>
       </c>
       <c r="R25" t="n">
-        <v>7235242</v>
+        <v>7235192</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3342,7 +3350,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3363,38 +3371,38 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891327</t>
+          <t>https://artportalen.se/Sighting/115891406</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115891441</v>
+        <v>115891218</v>
       </c>
       <c r="B26" t="n">
-        <v>79327</v>
+        <v>92732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2014</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3404,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538732</v>
+        <v>538546</v>
       </c>
       <c r="R26" t="n">
-        <v>7235164</v>
+        <v>7235286</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3453,7 +3461,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3474,38 +3482,38 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891441</t>
+          <t>https://artportalen.se/Sighting/115891218</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115891195</v>
+        <v>115891327</v>
       </c>
       <c r="B27" t="n">
-        <v>83307</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538796</v>
+        <v>538593</v>
       </c>
       <c r="R27" t="n">
-        <v>7235295</v>
+        <v>7235242</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3564,7 +3572,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3585,38 +3593,38 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891195</t>
+          <t>https://artportalen.se/Sighting/115891327</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115891395</v>
+        <v>115891441</v>
       </c>
       <c r="B28" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3626,10 +3634,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538761</v>
+        <v>538732</v>
       </c>
       <c r="R28" t="n">
-        <v>7235195</v>
+        <v>7235164</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3675,7 +3683,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3696,16 +3704,16 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891395</t>
+          <t>https://artportalen.se/Sighting/115891441</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>67152464</v>
+        <v>115891195</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3713,42 +3721,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Erikslund, Dikanäs, Ås lm</t>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538858</v>
+        <v>538796</v>
       </c>
       <c r="R29" t="n">
-        <v>7235106</v>
+        <v>7235295</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3772,12 +3775,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2017-08-05</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2017-08-05</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3788,20 +3791,247 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>6483</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115891195</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>115891395</v>
+      </c>
+      <c r="B30" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>538761</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7235195</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>6495</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115891395</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>67152464</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Erikslund, Dikanäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>538858</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7235106</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2017-08-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2017-08-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr">
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/67152464</t>
         </is>
@@ -3837,6 +4067,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -2932,7 +2932,7 @@
         <v>135653752</v>
       </c>
       <c r="B22" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2365,56 +2365,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135653739</v>
+        <v>115891382</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>5179</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dikafallet, Dikaån, Ås lm</t>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537660</v>
+        <v>538457</v>
       </c>
       <c r="R17" t="n">
-        <v>7234804</v>
+        <v>7235199</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2438,17 +2435,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2459,71 +2451,75 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>6358</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135653739</t>
+          <t>https://artportalen.se/Sighting/115891382</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115891382</v>
+        <v>115891158</v>
       </c>
       <c r="B18" t="n">
-        <v>5179</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538457</v>
+        <v>538366</v>
       </c>
       <c r="R18" t="n">
-        <v>7235199</v>
+        <v>7235312</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2569,7 +2565,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2590,16 +2586,16 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891382</t>
+          <t>https://artportalen.se/Sighting/115891158</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115891158</v>
+        <v>115891354</v>
       </c>
       <c r="B19" t="n">
-        <v>58114</v>
+        <v>58057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2607,21 +2603,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2627,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538366</v>
+        <v>538463</v>
       </c>
       <c r="R19" t="n">
-        <v>7235312</v>
+        <v>7235211</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2680,7 +2676,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2701,38 +2697,38 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891158</t>
+          <t>https://artportalen.se/Sighting/115891354</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115891354</v>
+        <v>115891250</v>
       </c>
       <c r="B20" t="n">
-        <v>58057</v>
+        <v>106229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2738,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538463</v>
+        <v>538270</v>
       </c>
       <c r="R20" t="n">
-        <v>7235211</v>
+        <v>7235272</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2791,7 +2787,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2812,38 +2808,38 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891354</t>
+          <t>https://artportalen.se/Sighting/115891250</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115891250</v>
+        <v>115891239</v>
       </c>
       <c r="B21" t="n">
-        <v>106229</v>
+        <v>97358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221725</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538270</v>
+        <v>538762</v>
       </c>
       <c r="R21" t="n">
-        <v>7235272</v>
+        <v>7235276</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2902,7 +2898,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2923,66 +2919,54 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891250</t>
+          <t>https://artportalen.se/Sighting/115891239</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135653752</v>
+        <v>115891394</v>
       </c>
       <c r="B22" t="n">
-        <v>99316</v>
+        <v>91905</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dikafallet, Dikaån, Ås lm</t>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537660</v>
+        <v>538608</v>
       </c>
       <c r="R22" t="n">
-        <v>7234804</v>
+        <v>7235196</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3006,12 +2990,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,34 +3004,42 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>6521</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Andreas Bernhold</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135653752</t>
+          <t>https://artportalen.se/Sighting/115891394</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115891239</v>
+        <v>115891406</v>
       </c>
       <c r="B23" t="n">
-        <v>97358</v>
+        <v>91905</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,21 +3047,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3079,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538762</v>
+        <v>538705</v>
       </c>
       <c r="R23" t="n">
-        <v>7235276</v>
+        <v>7235192</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3128,7 +3120,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3149,16 +3141,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891239</t>
+          <t>https://artportalen.se/Sighting/115891406</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115891394</v>
+        <v>115891218</v>
       </c>
       <c r="B24" t="n">
-        <v>91905</v>
+        <v>92732</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3166,21 +3158,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>2014</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3190,10 +3182,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538608</v>
+        <v>538546</v>
       </c>
       <c r="R24" t="n">
-        <v>7235196</v>
+        <v>7235286</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3239,7 +3231,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3260,38 +3252,38 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891394</t>
+          <t>https://artportalen.se/Sighting/115891218</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115891406</v>
+        <v>115891327</v>
       </c>
       <c r="B25" t="n">
-        <v>91905</v>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3293,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538705</v>
+        <v>538593</v>
       </c>
       <c r="R25" t="n">
-        <v>7235192</v>
+        <v>7235242</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3350,7 +3342,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3371,38 +3363,38 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891406</t>
+          <t>https://artportalen.se/Sighting/115891327</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115891218</v>
+        <v>115891441</v>
       </c>
       <c r="B26" t="n">
-        <v>92732</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2014</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3412,10 +3404,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538546</v>
+        <v>538732</v>
       </c>
       <c r="R26" t="n">
-        <v>7235286</v>
+        <v>7235164</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3461,7 +3453,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3482,38 +3474,38 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891218</t>
+          <t>https://artportalen.se/Sighting/115891441</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115891327</v>
+        <v>115891195</v>
       </c>
       <c r="B27" t="n">
-        <v>91872</v>
+        <v>83307</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3523,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538593</v>
+        <v>538796</v>
       </c>
       <c r="R27" t="n">
-        <v>7235242</v>
+        <v>7235295</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3572,7 +3564,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3593,38 +3585,38 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891327</t>
+          <t>https://artportalen.se/Sighting/115891195</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115891441</v>
+        <v>115891395</v>
       </c>
       <c r="B28" t="n">
-        <v>79327</v>
+        <v>83307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3634,10 +3626,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538732</v>
+        <v>538761</v>
       </c>
       <c r="R28" t="n">
-        <v>7235164</v>
+        <v>7235195</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3683,7 +3675,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3704,16 +3696,16 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891441</t>
+          <t>https://artportalen.se/Sighting/115891395</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115891195</v>
+        <v>67152464</v>
       </c>
       <c r="B29" t="n">
-        <v>83307</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3721,37 +3713,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Erikslund, Dikanäs, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538796</v>
+        <v>538858</v>
       </c>
       <c r="R29" t="n">
-        <v>7235295</v>
+        <v>7235106</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3775,12 +3772,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2017-08-05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2017-08-05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3791,247 +3788,20 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>6483</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/115891195</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>115891395</v>
-      </c>
-      <c r="B30" t="n">
-        <v>83307</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>538761</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7235195</v>
-      </c>
-      <c r="S30" t="n">
-        <v>5</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>6495</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/115891395</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>67152464</v>
-      </c>
-      <c r="B31" t="n">
-        <v>57953</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Erikslund, Dikanäs, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>538858</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7235106</v>
-      </c>
-      <c r="S31" t="n">
-        <v>25</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2017-08-05</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2017-08-05</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/67152464</t>
         </is>
@@ -4067,8 +3837,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2365,53 +2365,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115891382</v>
+        <v>135653739</v>
       </c>
       <c r="B17" t="n">
-        <v>5179</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Dikafallet, Dikaån, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538457</v>
+        <v>537660</v>
       </c>
       <c r="R17" t="n">
-        <v>7235199</v>
+        <v>7234804</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2435,12 +2438,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,75 +2459,71 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>6358</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891382</t>
+          <t>https://artportalen.se/Sighting/135653739</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115891158</v>
+        <v>115891382</v>
       </c>
       <c r="B18" t="n">
-        <v>58114</v>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538366</v>
+        <v>538457</v>
       </c>
       <c r="R18" t="n">
-        <v>7235312</v>
+        <v>7235199</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2565,7 +2569,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2586,16 +2590,16 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891158</t>
+          <t>https://artportalen.se/Sighting/115891382</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115891354</v>
+        <v>115891158</v>
       </c>
       <c r="B19" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2603,21 +2607,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2627,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538463</v>
+        <v>538366</v>
       </c>
       <c r="R19" t="n">
-        <v>7235211</v>
+        <v>7235312</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2697,38 +2701,38 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891354</t>
+          <t>https://artportalen.se/Sighting/115891158</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115891250</v>
+        <v>115891354</v>
       </c>
       <c r="B20" t="n">
-        <v>106229</v>
+        <v>58057</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2738,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538270</v>
+        <v>538463</v>
       </c>
       <c r="R20" t="n">
-        <v>7235272</v>
+        <v>7235211</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2787,7 +2791,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2808,38 +2812,38 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891250</t>
+          <t>https://artportalen.se/Sighting/115891354</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115891239</v>
+        <v>115891250</v>
       </c>
       <c r="B21" t="n">
-        <v>97358</v>
+        <v>106229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>221725</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538762</v>
+        <v>538270</v>
       </c>
       <c r="R21" t="n">
-        <v>7235276</v>
+        <v>7235272</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2898,7 +2902,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2919,54 +2923,66 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891239</t>
+          <t>https://artportalen.se/Sighting/115891250</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115891394</v>
+        <v>135653752</v>
       </c>
       <c r="B22" t="n">
-        <v>91905</v>
+        <v>99317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Dikafallet, Dikaån, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538608</v>
+        <v>537660</v>
       </c>
       <c r="R22" t="n">
-        <v>7235196</v>
+        <v>7234804</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,12 +3006,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,42 +3020,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>6521</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Andreas Bernhold</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891394</t>
+          <t>https://artportalen.se/Sighting/135653752</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115891406</v>
+        <v>115891239</v>
       </c>
       <c r="B23" t="n">
-        <v>91905</v>
+        <v>97358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,21 +3055,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3071,10 +3079,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538705</v>
+        <v>538762</v>
       </c>
       <c r="R23" t="n">
-        <v>7235192</v>
+        <v>7235276</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,7 +3128,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3141,16 +3149,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891406</t>
+          <t>https://artportalen.se/Sighting/115891239</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115891218</v>
+        <v>115891394</v>
       </c>
       <c r="B24" t="n">
-        <v>92732</v>
+        <v>91905</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3158,21 +3166,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2014</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3182,10 +3190,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538546</v>
+        <v>538608</v>
       </c>
       <c r="R24" t="n">
-        <v>7235286</v>
+        <v>7235196</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3231,7 +3239,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3252,38 +3260,38 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891218</t>
+          <t>https://artportalen.se/Sighting/115891394</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115891327</v>
+        <v>115891406</v>
       </c>
       <c r="B25" t="n">
-        <v>91872</v>
+        <v>91905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3293,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538593</v>
+        <v>538705</v>
       </c>
       <c r="R25" t="n">
-        <v>7235242</v>
+        <v>7235192</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3342,7 +3350,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3363,38 +3371,38 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891327</t>
+          <t>https://artportalen.se/Sighting/115891406</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115891441</v>
+        <v>115891218</v>
       </c>
       <c r="B26" t="n">
-        <v>79327</v>
+        <v>92732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2014</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3404,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538732</v>
+        <v>538546</v>
       </c>
       <c r="R26" t="n">
-        <v>7235164</v>
+        <v>7235286</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3453,7 +3461,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3474,38 +3482,38 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891441</t>
+          <t>https://artportalen.se/Sighting/115891218</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115891195</v>
+        <v>115891327</v>
       </c>
       <c r="B27" t="n">
-        <v>83307</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3523,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538796</v>
+        <v>538593</v>
       </c>
       <c r="R27" t="n">
-        <v>7235295</v>
+        <v>7235242</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3564,7 +3572,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3585,38 +3593,38 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891195</t>
+          <t>https://artportalen.se/Sighting/115891327</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115891395</v>
+        <v>115891441</v>
       </c>
       <c r="B28" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3626,10 +3634,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>538761</v>
+        <v>538732</v>
       </c>
       <c r="R28" t="n">
-        <v>7235195</v>
+        <v>7235164</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3675,7 +3683,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3696,16 +3704,16 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115891395</t>
+          <t>https://artportalen.se/Sighting/115891441</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>67152464</v>
+        <v>115891195</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3713,42 +3721,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Erikslund, Dikanäs, Ås lm</t>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>538858</v>
+        <v>538796</v>
       </c>
       <c r="R29" t="n">
-        <v>7235106</v>
+        <v>7235295</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3772,12 +3775,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2017-08-05</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2017-08-05</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3788,20 +3791,247 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>6483</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115891195</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>115891395</v>
+      </c>
+      <c r="B30" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>538761</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7235195</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>6495</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Rickard Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115891395</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>67152464</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Erikslund, Dikanäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>538858</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7235106</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2017-08-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2017-08-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Anton Gustafsson, Eino Kenttä, Johanna Eriksson, Ingemar Södergren, Linda Johannesson, Nils Ericson, Isak Vahlström</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr">
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/67152464</t>
         </is>
@@ -3837,6 +4067,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -2368,7 +2368,7 @@
         <v>135653739</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>135653752</v>
       </c>
       <c r="B22" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -2368,7 +2368,7 @@
         <v>135653739</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>135653752</v>
       </c>
       <c r="B22" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 9048-2023 artfynd.xlsx
+++ b/artfynd/A 9048-2023 artfynd.xlsx
@@ -2368,7 +2368,7 @@
         <v>135653739</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>135653752</v>
       </c>
       <c r="B22" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
